--- a/导入资料/下载.xlsx
+++ b/导入资料/下载.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26025" windowHeight="12855" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="基本信息" sheetId="1" r:id="rId1"/>
@@ -216,7 +216,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,13 +264,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -841,152 +834,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1015,13 +1008,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1030,23 +1023,20 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1414,7 +1404,7 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:8">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1424,139 +1414,139 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:8">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>20</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="22"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:8">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>21</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>22</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:8">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>23</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>24</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>25</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:8">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>26</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="19">
         <v>27</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="23" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1564,7 +1554,7 @@
       <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="12">
@@ -1576,15 +1566,13 @@
       <c r="E16" s="12">
         <v>385</v>
       </c>
-      <c r="F16" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6">
       <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="12">
@@ -1596,15 +1584,13 @@
       <c r="E17" s="12">
         <v>385</v>
       </c>
-      <c r="F17" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:6">
       <c r="A18" s="5">
         <v>3</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="12">
@@ -1616,15 +1602,13 @@
       <c r="E18" s="12">
         <v>385</v>
       </c>
-      <c r="F18" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F18" s="25"/>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:6">
       <c r="A19" s="5">
         <v>4</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
@@ -1636,15 +1620,13 @@
       <c r="E19" s="12">
         <v>385</v>
       </c>
-      <c r="F19" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F19" s="25"/>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6">
       <c r="A20" s="5">
         <v>5</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="12">
@@ -1656,15 +1638,13 @@
       <c r="E20" s="12">
         <v>385</v>
       </c>
-      <c r="F20" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F20" s="25"/>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:6">
       <c r="A21" s="5">
         <v>6</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="12">
@@ -1676,15 +1656,13 @@
       <c r="E21" s="12">
         <v>385</v>
       </c>
-      <c r="F21" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F21" s="25"/>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:6">
       <c r="A22" s="5">
         <v>7</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="12">
@@ -1696,9 +1674,7 @@
       <c r="E22" s="12">
         <v>385</v>
       </c>
-      <c r="F22" s="26">
-        <v>9.692907452</v>
-      </c>
+      <c r="F22" s="25"/>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:6">
       <c r="A23" s="5">
@@ -2561,27 +2537,27 @@
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6">
-      <c r="A68" s="24" t="s">
+      <c r="A68" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="D68" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F68" s="24" t="s">
+      <c r="F68" s="23" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4190,7 +4166,7 @@
       <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -4314,7 +4290,7 @@
       <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -4438,7 +4414,7 @@
       <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -4562,7 +4538,7 @@
       <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -4686,7 +4662,7 @@
       <c r="A19" s="10">
         <v>17</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -4810,7 +4786,7 @@
       <c r="A21" s="10">
         <v>19</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -4934,7 +4910,7 @@
       <c r="A23" s="10">
         <v>21</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -5058,7 +5034,7 @@
       <c r="A25" s="10">
         <v>23</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="10" t="s">
